--- a/Filtered/HCAFloridaAventura.xlsx
+++ b/Filtered/HCAFloridaAventura.xlsx
@@ -574,6 +574,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -626,6 +636,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -698,6 +718,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -750,6 +780,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -822,6 +862,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -874,6 +924,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -946,6 +1006,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -998,6 +1068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1070,6 +1150,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1122,6 +1212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1194,6 +1294,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1266,6 +1376,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1318,6 +1438,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1390,6 +1520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1442,6 +1582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1514,6 +1664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1566,6 +1726,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1638,6 +1808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1690,6 +1870,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1762,6 +1952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1814,6 +2014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1871,6 +2081,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1923,6 +2143,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1995,6 +2225,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2047,6 +2287,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2119,6 +2369,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2171,6 +2431,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2243,6 +2513,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2295,6 +2575,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2367,6 +2657,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2419,6 +2719,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2491,6 +2801,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2543,6 +2863,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2615,6 +2945,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2667,6 +3007,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2724,6 +3074,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2776,6 +3136,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2848,6 +3218,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2900,6 +3280,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2972,6 +3362,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3024,6 +3424,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3096,6 +3506,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3148,6 +3568,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3220,6 +3650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3272,6 +3712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3344,6 +3794,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3416,6 +3876,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3468,6 +3938,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3540,6 +4020,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3592,6 +4082,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3664,6 +4164,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3716,6 +4226,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3788,6 +4308,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3840,6 +4370,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3912,6 +4452,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3964,6 +4514,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4036,6 +4596,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4088,6 +4658,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4160,6 +4740,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4212,6 +4802,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4284,6 +4884,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4336,6 +4946,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4408,6 +5028,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4480,6 +5110,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +5172,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4604,6 +5254,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4656,6 +5316,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4713,6 +5383,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4765,6 +5445,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4837,6 +5527,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4889,6 +5589,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4961,6 +5671,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5013,6 +5733,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5085,6 +5815,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5137,6 +5877,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5209,6 +5959,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5261,6 +6021,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5333,6 +6103,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5385,6 +6165,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5457,6 +6247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5509,6 +6309,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5581,6 +6391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5633,6 +6453,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5705,6 +6535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5757,6 +6597,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5829,6 +6679,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5881,6 +6741,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5953,6 +6823,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6005,6 +6885,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6077,6 +6967,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6129,6 +7029,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6201,6 +7111,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6253,6 +7173,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6325,6 +7255,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6377,6 +7317,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6449,6 +7399,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6501,6 +7461,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6573,6 +7543,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6625,6 +7605,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6697,6 +7687,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6749,6 +7749,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6821,6 +7831,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6873,6 +7893,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6945,6 +7975,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6997,6 +8037,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7069,6 +8119,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7121,6 +8181,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7193,6 +8263,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7265,6 +8345,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7317,6 +8407,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7389,6 +8489,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7461,6 +8571,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7513,6 +8633,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7585,6 +8715,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7637,6 +8777,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7709,6 +8859,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7781,6 +8941,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7833,6 +9003,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7905,6 +9085,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7957,6 +9147,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8029,6 +9229,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8101,6 +9311,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8153,6 +9373,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8225,6 +9455,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8277,6 +9517,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8349,6 +9599,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8401,6 +9661,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8473,6 +9743,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8525,6 +9805,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8582,6 +9872,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8634,6 +9934,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8691,6 +10001,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8748,6 +10068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8800,6 +10130,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8872,6 +10212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8924,6 +10274,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8996,6 +10356,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9048,6 +10418,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9120,6 +10500,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9172,6 +10562,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9244,6 +10644,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9296,6 +10706,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9368,6 +10788,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9420,6 +10850,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9492,6 +10932,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9544,6 +10994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9616,6 +11076,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9668,6 +11138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9740,6 +11220,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9792,6 +11282,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9864,6 +11364,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9916,6 +11426,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9988,6 +11508,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10040,6 +11570,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10112,6 +11652,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10164,6 +11714,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10236,6 +11796,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10288,6 +11858,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10360,6 +11940,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10412,6 +12002,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10484,6 +12084,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10536,6 +12146,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10608,6 +12228,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10680,6 +12310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10732,6 +12372,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10804,6 +12454,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10856,6 +12516,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10913,6 +12583,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10965,6 +12645,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11022,6 +12712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11074,6 +12774,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11131,6 +12841,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11183,6 +12903,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11255,6 +12985,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11307,6 +13047,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11379,6 +13129,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11431,6 +13191,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11503,6 +13273,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11555,6 +13335,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11627,6 +13417,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11679,6 +13479,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11751,6 +13561,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11803,6 +13623,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11875,6 +13705,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11927,6 +13767,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11999,6 +13849,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12051,6 +13911,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12123,6 +13993,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12175,6 +14055,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12247,6 +14137,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12299,6 +14199,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12371,6 +14281,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12423,6 +14343,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12495,6 +14425,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12547,6 +14487,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12619,6 +14569,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12671,6 +14631,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12743,6 +14713,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12795,6 +14775,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12867,6 +14857,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12919,6 +14919,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12991,6 +15001,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13043,6 +15063,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13115,6 +15145,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13167,6 +15207,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13239,6 +15289,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13291,6 +15351,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13363,6 +15433,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13415,6 +15495,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13487,6 +15577,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13539,6 +15639,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13611,6 +15721,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13663,6 +15783,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13735,6 +15865,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13787,6 +15927,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13859,6 +16009,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13911,6 +16071,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13983,6 +16153,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14035,6 +16215,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14107,6 +16297,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14159,6 +16359,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14231,6 +16441,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14283,6 +16503,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14355,6 +16585,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14407,6 +16647,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14479,6 +16729,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14531,6 +16791,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14603,6 +16873,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14655,6 +16935,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14712,6 +17002,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14764,6 +17064,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14836,6 +17146,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14888,6 +17208,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14960,6 +17290,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15012,6 +17352,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15084,6 +17434,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15136,6 +17496,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15208,6 +17578,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15260,6 +17640,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15332,6 +17722,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15404,6 +17804,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15456,6 +17866,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15528,6 +17948,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15580,6 +18010,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15652,6 +18092,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15704,6 +18154,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15776,6 +18236,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15828,6 +18298,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15900,6 +18380,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15952,6 +18442,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16024,6 +18524,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16076,6 +18586,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16148,6 +18668,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16200,6 +18730,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16272,6 +18812,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16324,6 +18874,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16396,6 +18956,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16448,6 +19018,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16520,6 +19100,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16572,6 +19162,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16644,6 +19244,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16696,6 +19306,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16768,6 +19388,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16820,6 +19450,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16892,6 +19532,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16944,6 +19594,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17016,6 +19676,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17068,6 +19738,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17140,6 +19820,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17192,6 +19882,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17264,6 +19964,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17316,6 +20026,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17388,6 +20108,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17440,6 +20170,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17512,6 +20252,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17564,6 +20314,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17636,6 +20396,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17688,6 +20458,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17760,6 +20540,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17812,6 +20602,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17884,6 +20684,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17936,6 +20746,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18008,6 +20828,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18060,6 +20890,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18132,6 +20972,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18184,6 +21034,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18256,6 +21116,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18308,6 +21178,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18380,6 +21260,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18432,6 +21322,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18504,6 +21404,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18556,6 +21466,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18628,6 +21548,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18680,6 +21610,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18752,6 +21692,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18824,6 +21774,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18876,6 +21836,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18948,6 +21918,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19000,6 +21980,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19072,6 +22062,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19144,6 +22144,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19196,6 +22206,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19268,6 +22288,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19320,6 +22350,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19392,6 +22432,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19444,6 +22494,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19516,6 +22576,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19568,6 +22638,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19640,6 +22720,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19692,6 +22782,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19764,6 +22864,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19816,6 +22926,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19888,6 +23008,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19940,6 +23070,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20012,6 +23152,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20064,6 +23214,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20136,6 +23296,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20188,6 +23358,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20255,6 +23435,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20307,6 +23497,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20379,6 +23579,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20451,6 +23661,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20503,6 +23723,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20575,6 +23805,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20627,6 +23867,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20699,6 +23949,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20751,6 +24011,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20823,6 +24093,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20875,6 +24155,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20932,6 +24222,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20984,6 +24284,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21056,6 +24366,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21108,6 +24428,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21180,6 +24510,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21232,6 +24572,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21304,6 +24654,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21356,6 +24716,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21413,6 +24783,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21465,6 +24845,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21537,6 +24927,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21589,6 +24989,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21646,6 +25056,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21698,6 +25118,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21770,6 +25200,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21822,6 +25262,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21894,6 +25344,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21946,6 +25406,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22018,6 +25488,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22070,6 +25550,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22142,6 +25632,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22194,6 +25694,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22266,6 +25776,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22318,6 +25838,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22390,6 +25920,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22442,6 +25982,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22514,6 +26064,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22566,6 +26126,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22638,6 +26208,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22690,6 +26270,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22747,6 +26337,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22799,6 +26399,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22871,6 +26481,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22923,6 +26543,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22995,6 +26625,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23047,6 +26687,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23119,6 +26769,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23171,6 +26831,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23243,6 +26913,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23295,6 +26975,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23367,6 +27057,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23419,6 +27119,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23491,6 +27201,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23543,6 +27263,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23600,6 +27330,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23652,6 +27392,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23724,6 +27474,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23776,6 +27536,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23848,6 +27618,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23900,6 +27680,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23972,6 +27762,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24024,6 +27824,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24096,6 +27906,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24148,6 +27968,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24220,6 +28050,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24272,6 +28112,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24344,6 +28194,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24396,6 +28256,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24468,6 +28338,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24520,6 +28400,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24592,6 +28482,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24644,6 +28544,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24716,6 +28626,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24768,6 +28688,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24840,6 +28770,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24892,6 +28832,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24964,6 +28914,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25016,6 +28976,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25088,6 +29058,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25140,6 +29120,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25212,6 +29202,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25264,6 +29264,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25336,6 +29346,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25388,6 +29408,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25445,6 +29475,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25502,6 +29542,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25559,6 +29609,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25611,6 +29671,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25683,6 +29753,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25735,6 +29815,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25792,6 +29882,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25849,6 +29949,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25906,6 +30016,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25963,6 +30083,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26020,6 +30150,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26072,6 +30212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26144,6 +30294,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26196,6 +30356,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26268,6 +30438,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26320,6 +30500,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26392,6 +30582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26444,6 +30644,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26516,6 +30726,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26568,6 +30788,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26625,6 +30855,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26682,6 +30922,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26739,6 +30989,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26791,6 +31051,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26863,6 +31133,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26915,6 +31195,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26987,6 +31277,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27039,6 +31339,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27096,6 +31406,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27148,6 +31468,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27205,6 +31535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27262,6 +31602,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27314,6 +31664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27371,6 +31731,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27428,6 +31798,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27485,6 +31865,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27537,6 +31927,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27609,6 +32009,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27661,6 +32071,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27718,6 +32138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27775,6 +32205,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27832,6 +32272,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27884,6 +32334,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27956,6 +32416,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28008,6 +32478,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28065,6 +32545,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28117,6 +32607,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28189,6 +32689,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28241,6 +32751,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28298,6 +32818,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28355,6 +32885,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28412,6 +32952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28464,6 +33014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28536,6 +33096,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28588,6 +33158,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28660,6 +33240,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28712,6 +33302,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28769,6 +33369,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28826,6 +33436,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28878,6 +33498,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28935,6 +33565,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28992,6 +33632,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29049,6 +33699,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29099,6 +33759,16 @@
       <c r="J468" t="inlineStr">
         <is>
           <t>Acute</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>COCAT</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
